--- a/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/vida-util-rellenos-y-rotacion.xlsx
@@ -266,7 +266,7 @@
     </comment>
     <comment ref="J15" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1808/1991, de 13 de diciembre, por el que se regulan las menciones o marcas que permiten identificar el lote al que pertenece un producto alimenticio (BOE-A-1991-30... (Las tres vías: art. 2.2.b) (no envasado, envasado a petición del comprador o envasado para venta inmediata), art. 2... · https://www.boe.es/buscar/act.php?id=BOE-A-1991-30678</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1808/1991, de 13 de diciembre, por el que se regulan las menciones o marcas que permiten identificar el lote al que pertenece un producto alimenticio (BOE-A-1991-30... (Las tres vías: art. 2.2.b) (no envasado, envasado a petición del comprador o envasado para vent...) · https://www.boe.es/buscar/act.php?id=BOE-A-1991-30678</t>
       </text>
     </comment>
     <comment ref="A58" authorId="0" shapeId="0">
@@ -306,7 +306,7 @@
     </comment>
     <comment ref="G15" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1808/1991, de 13 de diciembre, por el que se regulan las menciones o marcas que permiten identificar el lote al que pertenece un producto alimenticio (BOE-A-1991-30... (Las tres vías: art. 2.2.b) (no envasado, envasado a petición del comprador o envasado para venta inmediata), art. 2... · https://www.boe.es/buscar/act.php?id=BOE-A-1991-30678</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1808/1991, de 13 de diciembre, por el que se regulan las menciones o marcas que permiten identificar el lote al que pertenece un producto alimenticio (BOE-A-1991-30... (Las tres vías: art. 2.2.b) (no envasado, envasado a petición del comprador o envasado para vent...) · https://www.boe.es/buscar/act.php?id=BOE-A-1991-30678</t>
       </text>
     </comment>
     <comment ref="I15" authorId="0" shapeId="0">
